--- a/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026_DEER_GENERAL_SEASON.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026_DEER_GENERAL_SEASON.xlsx
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N139"/>
+  <dimension ref="A1:O139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -535,6 +535,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -598,10 +599,15 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Average Harvest Age Prior Year</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
+          <t>Average Harvest Age</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Current Age (3-Yr Avg)</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>Avg Days Hunted Prior Year</t>
         </is>
@@ -665,7 +671,8 @@
         </is>
       </c>
       <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>9.5</t>
         </is>
@@ -729,7 +736,8 @@
         </is>
       </c>
       <c r="M5" s="6" t="inlineStr"/>
-      <c r="N5" s="6" t="inlineStr">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" s="6" t="inlineStr">
         <is>
           <t>8.2</t>
         </is>
@@ -793,7 +801,8 @@
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>7.7</t>
         </is>
@@ -857,7 +866,8 @@
         </is>
       </c>
       <c r="M7" s="6" t="inlineStr"/>
-      <c r="N7" s="6" t="inlineStr">
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" s="6" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
@@ -921,7 +931,8 @@
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr"/>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>7.3</t>
         </is>
@@ -985,7 +996,8 @@
         </is>
       </c>
       <c r="M9" s="6" t="inlineStr"/>
-      <c r="N9" s="6" t="inlineStr">
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" s="6" t="inlineStr">
         <is>
           <t>7.7</t>
         </is>
@@ -1049,7 +1061,8 @@
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr"/>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" s="4" t="inlineStr">
         <is>
           <t>6.1</t>
         </is>
@@ -1113,7 +1126,8 @@
         </is>
       </c>
       <c r="M11" s="6" t="inlineStr"/>
-      <c r="N11" s="6" t="inlineStr">
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" s="6" t="inlineStr">
         <is>
           <t>8.4</t>
         </is>
@@ -1177,7 +1191,8 @@
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr"/>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" s="4" t="inlineStr">
         <is>
           <t>7.3</t>
         </is>
@@ -1241,7 +1256,8 @@
         </is>
       </c>
       <c r="M13" s="6" t="inlineStr"/>
-      <c r="N13" s="6" t="inlineStr">
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" s="6" t="inlineStr">
         <is>
           <t>9.4</t>
         </is>
@@ -1305,7 +1321,8 @@
         </is>
       </c>
       <c r="M14" s="4" t="inlineStr"/>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" s="4" t="inlineStr">
         <is>
           <t>8.8</t>
         </is>
@@ -1369,7 +1386,8 @@
         </is>
       </c>
       <c r="M15" s="6" t="inlineStr"/>
-      <c r="N15" s="6" t="inlineStr">
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" s="6" t="inlineStr">
         <is>
           <t>9.3</t>
         </is>
@@ -1433,7 +1451,8 @@
         </is>
       </c>
       <c r="M16" s="4" t="inlineStr"/>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" s="4" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
@@ -1497,7 +1516,8 @@
         </is>
       </c>
       <c r="M17" s="6" t="inlineStr"/>
-      <c r="N17" s="6" t="inlineStr">
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" s="6" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
@@ -1561,7 +1581,8 @@
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr"/>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" s="4" t="inlineStr">
         <is>
           <t>7.2</t>
         </is>
@@ -1625,7 +1646,8 @@
         </is>
       </c>
       <c r="M19" s="6" t="inlineStr"/>
-      <c r="N19" s="6" t="inlineStr">
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -1689,7 +1711,8 @@
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr"/>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" s="4" t="inlineStr">
         <is>
           <t>6.4</t>
         </is>
@@ -1753,7 +1776,8 @@
         </is>
       </c>
       <c r="M21" s="6" t="inlineStr"/>
-      <c r="N21" s="6" t="inlineStr">
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" s="6" t="inlineStr">
         <is>
           <t>10.2</t>
         </is>
@@ -1817,7 +1841,8 @@
         </is>
       </c>
       <c r="M22" s="4" t="inlineStr"/>
-      <c r="N22" s="4" t="inlineStr">
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" s="4" t="inlineStr">
         <is>
           <t>10.4</t>
         </is>
@@ -1881,7 +1906,8 @@
         </is>
       </c>
       <c r="M23" s="6" t="inlineStr"/>
-      <c r="N23" s="6" t="inlineStr">
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" s="6" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
@@ -1945,7 +1971,8 @@
         </is>
       </c>
       <c r="M24" s="4" t="inlineStr"/>
-      <c r="N24" s="4" t="inlineStr">
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -2009,7 +2036,8 @@
         </is>
       </c>
       <c r="M25" s="6" t="inlineStr"/>
-      <c r="N25" s="6" t="inlineStr">
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" s="6" t="inlineStr">
         <is>
           <t>8.4</t>
         </is>
@@ -2073,7 +2101,8 @@
         </is>
       </c>
       <c r="M26" s="4" t="inlineStr"/>
-      <c r="N26" s="4" t="inlineStr">
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" s="4" t="inlineStr">
         <is>
           <t>7.6</t>
         </is>
@@ -2137,7 +2166,8 @@
         </is>
       </c>
       <c r="M27" s="6" t="inlineStr"/>
-      <c r="N27" s="6" t="inlineStr">
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" s="6" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
@@ -2201,7 +2231,8 @@
         </is>
       </c>
       <c r="M28" s="4" t="inlineStr"/>
-      <c r="N28" s="4" t="inlineStr">
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -2265,7 +2296,8 @@
         </is>
       </c>
       <c r="M29" s="6" t="inlineStr"/>
-      <c r="N29" s="6" t="inlineStr">
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" s="6" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
@@ -2329,7 +2361,8 @@
         </is>
       </c>
       <c r="M30" s="4" t="inlineStr"/>
-      <c r="N30" s="4" t="inlineStr">
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" s="4" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
@@ -2393,7 +2426,8 @@
         </is>
       </c>
       <c r="M31" s="6" t="inlineStr"/>
-      <c r="N31" s="6" t="inlineStr">
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -2457,7 +2491,8 @@
         </is>
       </c>
       <c r="M32" s="4" t="inlineStr"/>
-      <c r="N32" s="4" t="inlineStr">
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" s="4" t="inlineStr">
         <is>
           <t>3.9</t>
         </is>
@@ -2521,7 +2556,8 @@
         </is>
       </c>
       <c r="M33" s="6" t="inlineStr"/>
-      <c r="N33" s="6" t="inlineStr">
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" s="6" t="inlineStr">
         <is>
           <t>3.8</t>
         </is>
@@ -2585,7 +2621,8 @@
         </is>
       </c>
       <c r="M34" s="4" t="inlineStr"/>
-      <c r="N34" s="4" t="inlineStr">
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" s="4" t="inlineStr">
         <is>
           <t>3.9</t>
         </is>
@@ -2649,7 +2686,8 @@
         </is>
       </c>
       <c r="M35" s="6" t="inlineStr"/>
-      <c r="N35" s="6" t="inlineStr">
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" s="6" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
@@ -2713,7 +2751,8 @@
         </is>
       </c>
       <c r="M36" s="4" t="inlineStr"/>
-      <c r="N36" s="4" t="inlineStr">
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" s="4" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
@@ -2777,7 +2816,8 @@
         </is>
       </c>
       <c r="M37" s="6" t="inlineStr"/>
-      <c r="N37" s="6" t="inlineStr">
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" s="6" t="inlineStr">
         <is>
           <t>3.8</t>
         </is>
@@ -2841,7 +2881,8 @@
         </is>
       </c>
       <c r="M38" s="4" t="inlineStr"/>
-      <c r="N38" s="4" t="inlineStr">
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" s="4" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
@@ -2905,7 +2946,8 @@
         </is>
       </c>
       <c r="M39" s="6" t="inlineStr"/>
-      <c r="N39" s="6" t="inlineStr">
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" s="6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -2969,7 +3011,8 @@
         </is>
       </c>
       <c r="M40" s="4" t="inlineStr"/>
-      <c r="N40" s="4" t="inlineStr">
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" s="4" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
@@ -3033,7 +3076,8 @@
         </is>
       </c>
       <c r="M41" s="6" t="inlineStr"/>
-      <c r="N41" s="6" t="inlineStr">
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" s="6" t="inlineStr">
         <is>
           <t>3.9</t>
         </is>
@@ -3097,7 +3141,8 @@
         </is>
       </c>
       <c r="M42" s="4" t="inlineStr"/>
-      <c r="N42" s="4" t="inlineStr">
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" s="4" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
@@ -3161,7 +3206,8 @@
         </is>
       </c>
       <c r="M43" s="6" t="inlineStr"/>
-      <c r="N43" s="6" t="inlineStr">
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" s="6" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
@@ -3225,7 +3271,8 @@
         </is>
       </c>
       <c r="M44" s="4" t="inlineStr"/>
-      <c r="N44" s="4" t="inlineStr">
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" s="4" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
@@ -3289,7 +3336,8 @@
         </is>
       </c>
       <c r="M45" s="6" t="inlineStr"/>
-      <c r="N45" s="6" t="inlineStr">
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" s="6" t="inlineStr">
         <is>
           <t>3.9</t>
         </is>
@@ -3353,7 +3401,8 @@
         </is>
       </c>
       <c r="M46" s="4" t="inlineStr"/>
-      <c r="N46" s="4" t="inlineStr">
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" s="4" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
@@ -3417,7 +3466,8 @@
         </is>
       </c>
       <c r="M47" s="6" t="inlineStr"/>
-      <c r="N47" s="6" t="inlineStr">
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" s="6" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
@@ -3481,7 +3531,8 @@
         </is>
       </c>
       <c r="M48" s="4" t="inlineStr"/>
-      <c r="N48" s="4" t="inlineStr">
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" s="4" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
@@ -3545,7 +3596,8 @@
         </is>
       </c>
       <c r="M49" s="6" t="inlineStr"/>
-      <c r="N49" s="6" t="inlineStr">
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" s="6" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
@@ -3609,7 +3661,8 @@
         </is>
       </c>
       <c r="M50" s="4" t="inlineStr"/>
-      <c r="N50" s="4" t="inlineStr">
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" s="4" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
@@ -3673,7 +3726,8 @@
         </is>
       </c>
       <c r="M51" s="6" t="inlineStr"/>
-      <c r="N51" s="6" t="inlineStr">
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" s="6" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
@@ -3737,7 +3791,8 @@
         </is>
       </c>
       <c r="M52" s="4" t="inlineStr"/>
-      <c r="N52" s="4" t="inlineStr">
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" s="4" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
@@ -3801,7 +3856,8 @@
         </is>
       </c>
       <c r="M53" s="6" t="inlineStr"/>
-      <c r="N53" s="6" t="inlineStr">
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" s="6" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
@@ -3865,7 +3921,8 @@
         </is>
       </c>
       <c r="M54" s="4" t="inlineStr"/>
-      <c r="N54" s="4" t="inlineStr">
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" s="4" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
@@ -3929,7 +3986,8 @@
         </is>
       </c>
       <c r="M55" s="6" t="inlineStr"/>
-      <c r="N55" s="6" t="inlineStr">
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" s="6" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
@@ -3993,7 +4051,8 @@
         </is>
       </c>
       <c r="M56" s="4" t="inlineStr"/>
-      <c r="N56" s="4" t="inlineStr">
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" s="4" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
@@ -4057,7 +4116,8 @@
         </is>
       </c>
       <c r="M57" s="6" t="inlineStr"/>
-      <c r="N57" s="6" t="inlineStr">
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" s="6" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
@@ -4121,7 +4181,8 @@
         </is>
       </c>
       <c r="M58" s="4" t="inlineStr"/>
-      <c r="N58" s="4" t="inlineStr">
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" s="4" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
@@ -4185,7 +4246,8 @@
         </is>
       </c>
       <c r="M59" s="6" t="inlineStr"/>
-      <c r="N59" s="6" t="inlineStr">
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" s="6" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
@@ -4249,7 +4311,8 @@
         </is>
       </c>
       <c r="M60" s="4" t="inlineStr"/>
-      <c r="N60" s="4" t="inlineStr">
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" s="4" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
@@ -4313,7 +4376,8 @@
         </is>
       </c>
       <c r="M61" s="6" t="inlineStr"/>
-      <c r="N61" s="6" t="inlineStr">
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -4377,7 +4441,8 @@
         </is>
       </c>
       <c r="M62" s="4" t="inlineStr"/>
-      <c r="N62" s="4" t="inlineStr">
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -4441,7 +4506,8 @@
         </is>
       </c>
       <c r="M63" s="6" t="inlineStr"/>
-      <c r="N63" s="6" t="inlineStr">
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" s="6" t="inlineStr">
         <is>
           <t>3.9</t>
         </is>
@@ -4505,7 +4571,8 @@
         </is>
       </c>
       <c r="M64" s="4" t="inlineStr"/>
-      <c r="N64" s="4" t="inlineStr">
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" s="4" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
@@ -4569,7 +4636,8 @@
         </is>
       </c>
       <c r="M65" s="6" t="inlineStr"/>
-      <c r="N65" s="6" t="inlineStr">
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" s="6" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
@@ -4633,7 +4701,8 @@
         </is>
       </c>
       <c r="M66" s="4" t="inlineStr"/>
-      <c r="N66" s="4" t="inlineStr">
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" s="4" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
@@ -4697,7 +4766,8 @@
         </is>
       </c>
       <c r="M67" s="6" t="inlineStr"/>
-      <c r="N67" s="6" t="inlineStr">
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -4761,7 +4831,8 @@
         </is>
       </c>
       <c r="M68" s="4" t="inlineStr"/>
-      <c r="N68" s="4" t="inlineStr">
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" s="4" t="inlineStr">
         <is>
           <t>3.8</t>
         </is>
@@ -4825,7 +4896,8 @@
         </is>
       </c>
       <c r="M69" s="6" t="inlineStr"/>
-      <c r="N69" s="6" t="inlineStr">
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" s="6" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
@@ -4889,7 +4961,8 @@
         </is>
       </c>
       <c r="M70" s="4" t="inlineStr"/>
-      <c r="N70" s="4" t="inlineStr">
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" s="4" t="inlineStr">
         <is>
           <t>3.1</t>
         </is>
@@ -4953,7 +5026,8 @@
         </is>
       </c>
       <c r="M71" s="6" t="inlineStr"/>
-      <c r="N71" s="6" t="inlineStr">
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" s="6" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -5017,7 +5091,8 @@
         </is>
       </c>
       <c r="M72" s="4" t="inlineStr"/>
-      <c r="N72" s="4" t="inlineStr">
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" s="4" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
@@ -5081,7 +5156,8 @@
         </is>
       </c>
       <c r="M73" s="6" t="inlineStr"/>
-      <c r="N73" s="6" t="inlineStr">
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" s="6" t="inlineStr">
         <is>
           <t>3.6</t>
         </is>
@@ -5145,7 +5221,8 @@
         </is>
       </c>
       <c r="M74" s="4" t="inlineStr"/>
-      <c r="N74" s="4" t="inlineStr">
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" s="4" t="inlineStr">
         <is>
           <t>3.1</t>
         </is>
@@ -5209,7 +5286,8 @@
         </is>
       </c>
       <c r="M75" s="6" t="inlineStr"/>
-      <c r="N75" s="6" t="inlineStr">
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" s="6" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
@@ -5273,7 +5351,8 @@
         </is>
       </c>
       <c r="M76" s="4" t="inlineStr"/>
-      <c r="N76" s="4" t="inlineStr">
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" s="4" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -5337,7 +5416,8 @@
         </is>
       </c>
       <c r="M77" s="6" t="inlineStr"/>
-      <c r="N77" s="6" t="inlineStr">
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" s="6" t="inlineStr">
         <is>
           <t>3.8</t>
         </is>
@@ -5401,7 +5481,8 @@
         </is>
       </c>
       <c r="M78" s="4" t="inlineStr"/>
-      <c r="N78" s="4" t="inlineStr">
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" s="4" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
@@ -5465,7 +5546,8 @@
         </is>
       </c>
       <c r="M79" s="6" t="inlineStr"/>
-      <c r="N79" s="6" t="inlineStr">
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" s="6" t="inlineStr">
         <is>
           <t>2.9</t>
         </is>
@@ -5529,7 +5611,8 @@
         </is>
       </c>
       <c r="M80" s="4" t="inlineStr"/>
-      <c r="N80" s="4" t="inlineStr">
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -5593,7 +5676,8 @@
         </is>
       </c>
       <c r="M81" s="6" t="inlineStr"/>
-      <c r="N81" s="6" t="inlineStr">
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" s="6" t="inlineStr">
         <is>
           <t>3.8</t>
         </is>
@@ -5657,7 +5741,8 @@
         </is>
       </c>
       <c r="M82" s="4" t="inlineStr"/>
-      <c r="N82" s="4" t="inlineStr">
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" s="4" t="inlineStr">
         <is>
           <t>8.8</t>
         </is>
@@ -5721,7 +5806,8 @@
         </is>
       </c>
       <c r="M83" s="6" t="inlineStr"/>
-      <c r="N83" s="6" t="inlineStr">
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -5785,7 +5871,8 @@
         </is>
       </c>
       <c r="M84" s="4" t="inlineStr"/>
-      <c r="N84" s="4" t="inlineStr">
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" s="4" t="inlineStr">
         <is>
           <t>3.6</t>
         </is>
@@ -5849,7 +5936,8 @@
         </is>
       </c>
       <c r="M85" s="6" t="inlineStr"/>
-      <c r="N85" s="6" t="inlineStr">
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" s="6" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
@@ -5913,7 +6001,8 @@
         </is>
       </c>
       <c r="M86" s="4" t="inlineStr"/>
-      <c r="N86" s="4" t="inlineStr">
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" s="4" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
@@ -5977,7 +6066,8 @@
         </is>
       </c>
       <c r="M87" s="6" t="inlineStr"/>
-      <c r="N87" s="6" t="inlineStr">
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -6041,7 +6131,8 @@
         </is>
       </c>
       <c r="M88" s="4" t="inlineStr"/>
-      <c r="N88" s="4" t="inlineStr">
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" s="4" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
@@ -6105,7 +6196,8 @@
         </is>
       </c>
       <c r="M89" s="6" t="inlineStr"/>
-      <c r="N89" s="6" t="inlineStr">
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" s="6" t="inlineStr">
         <is>
           <t>7.6</t>
         </is>
@@ -6169,7 +6261,8 @@
         </is>
       </c>
       <c r="M90" s="4" t="inlineStr"/>
-      <c r="N90" s="4" t="inlineStr">
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" s="4" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
@@ -6233,7 +6326,8 @@
         </is>
       </c>
       <c r="M91" s="6" t="inlineStr"/>
-      <c r="N91" s="6" t="inlineStr">
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" s="6" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
@@ -6297,7 +6391,8 @@
         </is>
       </c>
       <c r="M92" s="4" t="inlineStr"/>
-      <c r="N92" s="4" t="inlineStr">
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" s="4" t="inlineStr">
         <is>
           <t>9.5</t>
         </is>
@@ -6361,7 +6456,8 @@
         </is>
       </c>
       <c r="M93" s="6" t="inlineStr"/>
-      <c r="N93" s="6" t="inlineStr">
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" s="6" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
@@ -6425,7 +6521,8 @@
         </is>
       </c>
       <c r="M94" s="4" t="inlineStr"/>
-      <c r="N94" s="4" t="inlineStr">
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" s="4" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
@@ -6489,7 +6586,8 @@
         </is>
       </c>
       <c r="M95" s="6" t="inlineStr"/>
-      <c r="N95" s="6" t="inlineStr">
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" s="6" t="inlineStr">
         <is>
           <t>9.1</t>
         </is>
@@ -6553,7 +6651,8 @@
         </is>
       </c>
       <c r="M96" s="4" t="inlineStr"/>
-      <c r="N96" s="4" t="inlineStr">
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" s="4" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
@@ -6617,7 +6716,8 @@
         </is>
       </c>
       <c r="M97" s="6" t="inlineStr"/>
-      <c r="N97" s="6" t="inlineStr">
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" s="6" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
@@ -6681,7 +6781,8 @@
         </is>
       </c>
       <c r="M98" s="4" t="inlineStr"/>
-      <c r="N98" s="4" t="inlineStr">
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" s="4" t="inlineStr">
         <is>
           <t>8.9</t>
         </is>
@@ -6745,7 +6846,8 @@
         </is>
       </c>
       <c r="M99" s="6" t="inlineStr"/>
-      <c r="N99" s="6" t="inlineStr">
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" s="6" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
@@ -6809,7 +6911,8 @@
         </is>
       </c>
       <c r="M100" s="4" t="inlineStr"/>
-      <c r="N100" s="4" t="inlineStr">
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -6873,7 +6976,8 @@
         </is>
       </c>
       <c r="M101" s="6" t="inlineStr"/>
-      <c r="N101" s="6" t="inlineStr">
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" s="6" t="inlineStr">
         <is>
           <t>7.9</t>
         </is>
@@ -6937,7 +7041,8 @@
         </is>
       </c>
       <c r="M102" s="4" t="inlineStr"/>
-      <c r="N102" s="4" t="inlineStr">
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" s="4" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
@@ -7001,7 +7106,8 @@
         </is>
       </c>
       <c r="M103" s="6" t="inlineStr"/>
-      <c r="N103" s="6" t="inlineStr">
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" s="6" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
@@ -7065,7 +7171,8 @@
         </is>
       </c>
       <c r="M104" s="4" t="inlineStr"/>
-      <c r="N104" s="4" t="inlineStr">
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" s="4" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
@@ -7129,7 +7236,8 @@
         </is>
       </c>
       <c r="M105" s="6" t="inlineStr"/>
-      <c r="N105" s="6" t="inlineStr">
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" s="6" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
@@ -7193,7 +7301,8 @@
         </is>
       </c>
       <c r="M106" s="4" t="inlineStr"/>
-      <c r="N106" s="4" t="inlineStr">
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" s="4" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
@@ -7257,7 +7366,8 @@
         </is>
       </c>
       <c r="M107" s="6" t="inlineStr"/>
-      <c r="N107" s="6" t="inlineStr">
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" s="6" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
@@ -7321,7 +7431,8 @@
         </is>
       </c>
       <c r="M108" s="4" t="inlineStr"/>
-      <c r="N108" s="4" t="inlineStr">
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" s="4" t="inlineStr">
         <is>
           <t>3.1</t>
         </is>
@@ -7385,7 +7496,8 @@
         </is>
       </c>
       <c r="M109" s="6" t="inlineStr"/>
-      <c r="N109" s="6" t="inlineStr">
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" s="6" t="inlineStr">
         <is>
           <t>9.9</t>
         </is>
@@ -7449,7 +7561,8 @@
         </is>
       </c>
       <c r="M110" s="4" t="inlineStr"/>
-      <c r="N110" s="4" t="inlineStr">
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" s="4" t="inlineStr">
         <is>
           <t>9.9</t>
         </is>
@@ -7513,7 +7626,8 @@
         </is>
       </c>
       <c r="M111" s="6" t="inlineStr"/>
-      <c r="N111" s="6" t="inlineStr">
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" s="6" t="inlineStr">
         <is>
           <t>9.7</t>
         </is>
@@ -7577,7 +7691,8 @@
         </is>
       </c>
       <c r="M112" s="4" t="inlineStr"/>
-      <c r="N112" s="4" t="inlineStr">
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" s="4" t="inlineStr">
         <is>
           <t>10.2</t>
         </is>
@@ -7641,7 +7756,8 @@
         </is>
       </c>
       <c r="M113" s="6" t="inlineStr"/>
-      <c r="N113" s="6" t="inlineStr">
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" s="6" t="inlineStr">
         <is>
           <t>10.6</t>
         </is>
@@ -7705,7 +7821,8 @@
         </is>
       </c>
       <c r="M114" s="4" t="inlineStr"/>
-      <c r="N114" s="4" t="inlineStr">
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" s="4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -7769,7 +7886,8 @@
         </is>
       </c>
       <c r="M115" s="6" t="inlineStr"/>
-      <c r="N115" s="6" t="inlineStr">
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" s="6" t="inlineStr">
         <is>
           <t>9.4</t>
         </is>
@@ -7833,7 +7951,8 @@
         </is>
       </c>
       <c r="M116" s="4" t="inlineStr"/>
-      <c r="N116" s="4" t="inlineStr">
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" s="4" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
@@ -7897,7 +8016,8 @@
         </is>
       </c>
       <c r="M117" s="6" t="inlineStr"/>
-      <c r="N117" s="6" t="inlineStr">
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" s="6" t="inlineStr">
         <is>
           <t>7.2</t>
         </is>
@@ -7961,7 +8081,8 @@
         </is>
       </c>
       <c r="M118" s="4" t="inlineStr"/>
-      <c r="N118" s="4" t="inlineStr">
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" s="4" t="inlineStr">
         <is>
           <t>11.6</t>
         </is>
@@ -8025,7 +8146,8 @@
         </is>
       </c>
       <c r="M119" s="6" t="inlineStr"/>
-      <c r="N119" s="6" t="inlineStr">
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" s="6" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
@@ -8089,7 +8211,8 @@
         </is>
       </c>
       <c r="M120" s="4" t="inlineStr"/>
-      <c r="N120" s="4" t="inlineStr">
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" s="4" t="inlineStr">
         <is>
           <t>11.6</t>
         </is>
@@ -8153,7 +8276,8 @@
         </is>
       </c>
       <c r="M121" s="6" t="inlineStr"/>
-      <c r="N121" s="6" t="inlineStr">
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" s="6" t="inlineStr">
         <is>
           <t>11.5</t>
         </is>
@@ -8217,7 +8341,8 @@
         </is>
       </c>
       <c r="M122" s="4" t="inlineStr"/>
-      <c r="N122" s="4" t="inlineStr">
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" s="4" t="inlineStr">
         <is>
           <t>10.1</t>
         </is>
@@ -8281,7 +8406,8 @@
         </is>
       </c>
       <c r="M123" s="6" t="inlineStr"/>
-      <c r="N123" s="6" t="inlineStr">
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" s="6" t="inlineStr">
         <is>
           <t>9.4</t>
         </is>
@@ -8345,7 +8471,8 @@
         </is>
       </c>
       <c r="M124" s="4" t="inlineStr"/>
-      <c r="N124" s="4" t="inlineStr">
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" s="4" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
@@ -8409,7 +8536,8 @@
         </is>
       </c>
       <c r="M125" s="6" t="inlineStr"/>
-      <c r="N125" s="6" t="inlineStr">
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" s="6" t="inlineStr">
         <is>
           <t>8.9</t>
         </is>
@@ -8473,7 +8601,8 @@
         </is>
       </c>
       <c r="M126" s="4" t="inlineStr"/>
-      <c r="N126" s="4" t="inlineStr">
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" s="4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -8537,7 +8666,8 @@
         </is>
       </c>
       <c r="M127" s="6" t="inlineStr"/>
-      <c r="N127" s="6" t="inlineStr">
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" s="6" t="inlineStr">
         <is>
           <t>8.2</t>
         </is>
@@ -8601,7 +8731,8 @@
         </is>
       </c>
       <c r="M128" s="4" t="inlineStr"/>
-      <c r="N128" s="4" t="inlineStr">
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" s="4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -8665,7 +8796,8 @@
         </is>
       </c>
       <c r="M129" s="6" t="inlineStr"/>
-      <c r="N129" s="6" t="inlineStr">
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" s="6" t="inlineStr">
         <is>
           <t>9.4</t>
         </is>
@@ -8729,7 +8861,8 @@
         </is>
       </c>
       <c r="M130" s="4" t="inlineStr"/>
-      <c r="N130" s="4" t="inlineStr">
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" s="4" t="inlineStr">
         <is>
           <t>9.3</t>
         </is>
@@ -8793,7 +8926,8 @@
         </is>
       </c>
       <c r="M131" s="6" t="inlineStr"/>
-      <c r="N131" s="6" t="inlineStr">
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" s="6" t="inlineStr">
         <is>
           <t>8.2</t>
         </is>
@@ -8857,7 +8991,8 @@
         </is>
       </c>
       <c r="M132" s="4" t="inlineStr"/>
-      <c r="N132" s="4" t="inlineStr">
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" s="4" t="inlineStr">
         <is>
           <t>10.7</t>
         </is>
@@ -8921,7 +9056,8 @@
         </is>
       </c>
       <c r="M133" s="6" t="inlineStr"/>
-      <c r="N133" s="6" t="inlineStr">
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" s="6" t="inlineStr">
         <is>
           <t>10.8</t>
         </is>
@@ -8985,7 +9121,8 @@
         </is>
       </c>
       <c r="M134" s="4" t="inlineStr"/>
-      <c r="N134" s="4" t="inlineStr">
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" s="4" t="inlineStr">
         <is>
           <t>8.7</t>
         </is>
@@ -9049,7 +9186,8 @@
         </is>
       </c>
       <c r="M135" s="6" t="inlineStr"/>
-      <c r="N135" s="6" t="inlineStr">
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" s="6" t="inlineStr">
         <is>
           <t>8.2</t>
         </is>
@@ -9113,7 +9251,8 @@
         </is>
       </c>
       <c r="M136" s="4" t="inlineStr"/>
-      <c r="N136" s="4" t="inlineStr">
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" s="4" t="inlineStr">
         <is>
           <t>11.7</t>
         </is>
@@ -9177,7 +9316,8 @@
         </is>
       </c>
       <c r="M137" s="6" t="inlineStr"/>
-      <c r="N137" s="6" t="inlineStr">
+      <c r="N137" t="inlineStr"/>
+      <c r="O137" s="6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -9241,7 +9381,8 @@
         </is>
       </c>
       <c r="M138" s="4" t="inlineStr"/>
-      <c r="N138" s="4" t="inlineStr">
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" s="4" t="inlineStr">
         <is>
           <t>9.1</t>
         </is>
@@ -9305,7 +9446,8 @@
         </is>
       </c>
       <c r="M139" s="6" t="inlineStr"/>
-      <c r="N139" s="6" t="inlineStr">
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" s="6" t="inlineStr">
         <is>
           <t>9.8</t>
         </is>
